--- a/runs/RELX/2026-10-14/bear/scratch/s_stack_324_no_wacc_shift/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/s_stack_324_no_wacc_shift/out/dcf.xlsx
@@ -539,11 +539,11 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.09088541398076617</v>
+        <v>0.09376215918747212</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PM rule: return on new investment 9.6% (value driver formula, briefs/RELX.yaml)</t>
+          <t>PM rule: return on new investment 8.9% (value driver formula, briefs/RELX.yaml)</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1471.811923278785</v>
+        <v>1513.5188399212</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.103145</v>
+        <v>0.0953618</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.09615342190000001</v>
+        <v>0.089367872476</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>8367.04257032339</v>
+        <v>8491.715205383671</v>
       </c>
     </row>
     <row r="21">
@@ -1448,7 +1448,7 @@
         <v/>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2313.223938384636</v>
+        <v>2280.762170272356</v>
       </c>
     </row>
     <row r="22">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>28504.330245434</v>
+        <v>30668.64889819732</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>18857.74649664404</v>
+        <v>20864.55422309283</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>27224.78906696743</v>
+        <v>29356.2694284765</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>20227.78906696743</v>
+        <v>22359.2694284765</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>18571.87886648285</v>
+        <v>20740.18342280381</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>10.65051098008169</v>
+        <v>11.89397975625033</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1065.051098008169</v>
+        <v>1189.397975625033</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.6156437755</v>
+        <v>-0.5707694061</v>
       </c>
     </row>
   </sheetData>
